--- a/excel/Mac平台Edge全量快捷键.xlsx
+++ b/excel/Mac平台Edge全量快捷键.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415A0559-F9B3-4217-833F-07BE4C71CBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="120">
   <si>
     <t>快捷键组合</t>
   </si>
@@ -379,13 +380,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -412,15 +419,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C9AE8A3-5514-4FAD-B9E2-D7593B7B9323}" name="表1" displayName="表1" ref="A1:B61" totalsRowShown="0">
+  <autoFilter ref="A1:B61" xr:uid="{1C9AE8A3-5514-4FAD-B9E2-D7593B7B9323}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{8FEC7DF6-4C83-4F31-A825-977FADA9528B}" name="快捷键组合"/>
+    <tableColumn id="2" xr3:uid="{1ED15926-BAD5-48E3-836C-FC449EC02D7B}" name="对应功能说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -676,15 +705,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="43"/>
-    <col customWidth="true" max="2" min="2" width="50"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="77.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -692,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -700,7 +729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -708,7 +737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -716,7 +745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -724,7 +753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -732,7 +761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -740,7 +769,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -748,7 +777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -756,7 +785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -764,7 +793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -772,7 +801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -780,7 +809,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -788,7 +817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -796,7 +825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -804,7 +833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -812,7 +841,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -820,7 +849,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -828,7 +857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -836,7 +865,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -844,7 +873,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -852,7 +881,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -860,7 +889,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -868,7 +897,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -876,7 +905,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -884,7 +913,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -892,7 +921,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -900,7 +929,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -908,7 +937,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -916,7 +945,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -924,7 +953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -932,7 +961,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -940,7 +969,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -948,7 +977,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -956,7 +985,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -964,7 +993,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -972,7 +1001,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -980,7 +1009,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -988,7 +1017,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -996,7 +1025,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -1004,7 +1033,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -1012,7 +1041,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -1020,7 +1049,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -1028,7 +1057,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -1036,7 +1065,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -1044,7 +1073,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1052,7 +1081,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -1060,7 +1089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1068,7 +1097,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -1076,7 +1105,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1084,7 +1113,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -1092,7 +1121,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -1100,7 +1129,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1108,7 +1137,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -1116,7 +1145,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -1124,7 +1153,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -1132,7 +1161,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -1140,7 +1169,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -1148,7 +1177,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -1156,7 +1185,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -1164,7 +1193,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>119</v>
       </c>
@@ -1173,5 +1202,10 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>